--- a/src/main/resources/static/excel/toktok.xlsx
+++ b/src/main/resources/static/excel/toktok.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jeongchanmin/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7498ADE1-65B4-1C48-B7B4-D9C1A421ACA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7D5D3CD-4C33-ED4D-ADFF-32DB066F6686}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="640" yWindow="740" windowWidth="28100" windowHeight="17120" xr2:uid="{D9A326C4-B758-E849-A9AE-141158099DC7}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="63">
   <si>
     <t>title</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -56,7 +56,249 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>imageId</t>
+    <t>"소비자 심리지수는 왜 중요한가?"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>소비자 심리지수는 사람들이 경제 상황을 어떻게 느끼고 있는지를 보여주는 지표예요. 이 지수가 높으면 소비자들이 경제를 긍정적으로 보고 소비를 늘릴 가능성이 커지고, 낮으면 소비를 줄이며 경제 활동이 위축될 수 있어요.
+예를 들어, 심리지수가 높을 땐 가전제품이나 자동차 같은 큰 소비가 늘고, 낮을 땐 절약 경향이 강해질 수 있어요. 이처럼 소비자 심리가 경제 전체에 큰 영향을 미치기 때문에 매우 중요합니다.
+그렇다면 현재 소비자 심리는 어떤 상태라고 생각하시는지 여러분의 의견을 남겨주세요!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"고용 지표로 보는 경제 상황"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>고용 지표는 경제의 건강 상태를 보여주는 중요한 수치예요. 고용률이 높고 실업률이 낮다면 경제가 안정적이고 활발하다는 신호로 볼 수 있죠. 반대로 실업률이 높아지면 소비가 줄고 기업 활동도 위축될 가능성이 커요.
+예를 들어, 신입 채용이 늘고 일자리가 많아지는 상황은 경제 회복이나 성장의 신호일 수 있습니다. 고용 지표는 기업, 정부, 가계가 경제 상황을 판단하고 대응하는 데 중요한 역할을 해요.
+그렇다면 여러분은 현재의 고용 상황이 경제에 어떤 영향을 미친다고 생각하시나요?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"소비 트렌드 변화가 경제에 미치는 영향"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>소비 트렌드는 사람들이 무엇을 사고 어떻게 소비하는지를 보여주는 중요한 지표예요. 최근 온라인 쇼핑이 늘어나면서 오프라인 매장은 줄어들고 물류 산업이 성장하고 있어요. 또한, 친환경 제품을 선호하는 소비자들이 많아지면서 관련 산업이 활성화되고 있어요.
+이러한 변화는 기업의 생산과 마케팅 전략뿐만 아니라 고용 구조에도 영향을 미쳐요. 소비 트렌드의 변화는 경제 구조를 바꾸는 중요한 요인인데요, 그렇다면 여러분은 현재 어떤 소비 트렌드가 경제에 가장 큰 영향을 주고 있다고 생각하시나요?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"적금 vs. 주식: 어떤 금융상품이 더 유리할까?"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>적금과 주식은 성격이 다른 금융상품으로, 각자의 장단점이 있어요. 적금은 원금이 보장되고 안정적이라 큰 위험 없이 돈을 모으기에 적합하지만, 수익률이 낮은 편이에요. 반면, 주식은 높은 수익을 기대할 수 있지만 손실 위험도 크기 때문에 신중한 선택이 필요해요. 예를 들어, 매달 꾸준히 돈을 모아 목표를 달성하려면 적금이 적합하고, 장기적으로 자산을 불리고 싶다면 주식이 더 나을 수 있어요. 
+적금과 주식 중 어떤 선택이 더 유리할지는 개인의 재정 상황과 목표에 따라 다를 텐데요, 여러분은 어떤 금융상품이 더 적합하다고 생각하시나요?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"개인 금융 앱, 얼마나 유용할까?"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>개인 금융 앱은 가계부 관리, 예산 설정, 투자, 자산 추적 등 다양한 기능을 제공해 재정 관리를 더 쉽게 만들어줘요. 가계부 앱은 월별 지출과 수입을 한눈에 파악하게 해 주고, 투자 앱은 주식, 펀드 등의 자산을 관리하는 데 도움을 줘요.
+이런 앱들은 시간을 절약하고 효율성을 높여주지만, 보안 문제나 사용자의 습관에 따라 만족도가 달라질 수 있어요. 여러분은 어떤 금융 앱을 사용하고 계신가요? 실제로 유용했던 기능이나 추천할 만한 앱이 있다면 공유해주세요!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"퇴직연금, 어떻게 준비해야 할까?"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>퇴직연금은 은퇴 후 안정적인 생활을 위한 중요한 재정 자산이에요. 준비할 때는 안정성과 수익성을 균형 있게 고려해야 해요. 예를 들어, 원금 보장이 되는 예금이나 채권에 투자하면 안전하지만 수익률이 낮고, 주식이나 펀드에 투자하면 높은 수익을 기대할 수 있지만 위험이 따르죠. 장기적인 관점에서 복리 효과를 활용하면 작은 차이가 큰 결과로 이어질 수 있어요. 또한, 연금 자산을 분산 투자해 리스크를 관리하는 것도 중요해요. 퇴직 후를 대비한 효과적인 연금 관리와 투자 전략, 여러분은 어떻게 준비하고 계신가요?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"신용등급 올리기: 꿀팁 공유"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>신용등급은 금융 신뢰도를 보여주는 중요한 지표로, 대출 금리, 신용카드 발급, 금융상품 이용 등에서 큰 영향을 미쳐요. 신용등급을 높이기 위해선 카드 대금과 대출을 제때 상환하고, 카드 한도를 적정 수준으로 유지하며, 과도한 신용 조회를 피하는 것이 중요해요. 
+예를 들어, 소액이라도 꾸준히 신용카드를 사용하고 연체 없이 납부하면 등급 개선에 긍정적인 영향을 줄 수 있어요. 신용 관리는 미래 금융 계획의 핵심인데요, 여러분은 신용등급을 올리기 위해 어떤 실천을 하고 계신가요? 꿀팁을 나눠주세요!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"해외 여행 비용, 환율에 따라 얼마나 달라질까?"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>환율은 해외여행 비용에 직접적인 영향을 미쳐요. 환율이 오르면 항공권, 숙박비, 현지 소비 비용이 늘어나고, 환율이 내리면 여행 경비를 절약할 수 있죠. 예를 들어, 환율이 낮을 때 미리 환전을 하거나 은행의 환율 우대 혜택을 활용하면 비용을 줄일 수 있어요.
+또, 환율 변동이 큰 시기에는 소액만 환전하고, 현지에서 신용카드를 활용해 결제하는 방법도 효과적이에요. 환율 변동을 이해하고 대처하는 것은 여행 경비를 관리하는 데 중요한데요, 여러분은 환율 변화에 어떻게 대응하고 계신가요? 경험과 팁을 공유해주세요!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>imageUrl</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"글로벌 경제 지표를 읽는 방법"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GDP, 무역수지, 실업률 같은 글로벌 경제 지표는 경제 상황을 이해하는 데 중요한 역할을 해요. GDP가 증가하면 경제가 성장하고 있다는 신호이고, 무역수지가 적자라면 수출보다 수입이 많아 경제에 부담을 줄 수 있어요. 실업률은 고용 상황을 나타내며 경제 안정성을 보여줘요. 
+예를 들어, GDP 상승은 소비와 투자의 증가를 의미하고, 낮은 실업률은 경제 활황의 신호일 수 있어요. 이런 지표를 이해하면 글로벌 경제 흐름을 더 잘 파악할 수 있는데요, 여러분은 어떤 경제 지표를 가장 중요하게 생각하시나요? 이유를 함께 공유해주세요!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"주요국 경제 정책 트렌드 비교"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>주요국의 경제 정책은 각국의 상황과 목표에 따라 다르게 설계되며, 글로벌 경제에 큰 영향을 미쳐요. 예를 들어, 미국은 금리 인상을 통해 인플레이션 억제를 우선시할 수 있고, 유럽은 친환경 산업 육성을 목표로 정책을 추진할 수 있어요. 또, 아시아 국가들은 기술 혁신과 제조업 강화를 중심으로 경제 성장을 도모하기도 하죠. 이러한 정책 트렌드를 비교하면 각국의 경제 전략과 글로벌 시장의 흐름을 이해하는 데 도움이 돼요. 여러분은 어떤 국가의 경제 정책이 주목할 만하다고 생각하시나요? 그 이유를 함께 논의해보세요!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"수출입 변화가 지역 경제에 미치는 영향"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>수출입은 지역 경제에 큰 영향을 미치는 요소예요. 수출이 증가하면 지역 기업의 매출이 늘고 고용 창출로 이어질 수 있지만, 수입이 늘어나면 국내 기업이 경쟁력을 잃을 수도 있어요. 예를 들어, 특정 지역에서 주요 수출품의 수요가 감소하면 해당 산업이 위축되고 지역 경제가 어려움을 겪을 수 있어요. 반대로, 새로운 수출 시장이 열리면 지역 산업이 성장하고 경제 활성화로 이어질 수 있죠. 수출입 구조 변화는 어떤 방식으로 지역 경제를 바꾸고 있을까요? 여러분의 의견을 나눠주세요!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"부동산 데이터, 어떻게 활용할까?"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>부동산 데이터는 집값, 거래량, 전세 가격, 입지 조건 등 다양한 정보를 담고 있어요. 이 데이터를 활용하면 주택 구매나 투자 결정을 더 현명하게 내릴 수 있어요. 예를 들어, 지역별 시세 변동을 분석하면 적절한 구매 시점을 파악할 수 있고, 입지 조건 데이터를 통해 실거주와 투자에 적합한 지역을 선택할 수 있죠. 부동산 데이터를 어떻게 활용하느냐에 따라 경제적 이익과 리스크 관리가 달라질 수 있어요. 여러분은 부동산 데이터를 어떤 방식으로 활용하고 계신가요? 경험을 공유해주세요!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"전세와 월세, 어떤 선택이 더 현명할까?"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>전세와 월세는 각각 장단점이 있어 상황에 따라 다른 선택이 필요해요. 전세는 월세 부담이 없어 안정적이지만, 초기 비용이 많이 들고 전세금을 묶어둬야 해요. 반면, 월세는 초기 비용이 적고 유동적인 생활이 가능하지만, 매달 고정적인 지출이 필요해요. 예를 들어, 장기 거주를 계획한다면 전세가 유리할 수 있고, 단기 거주나 자금 유동성이 중요하다면 월세가 더 나을 수 있어요. 여러분은 전세와 월세 중 어떤 선택을 하고 계신가요? 그 이유와 경험을 공유해주세요!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"부동산 시장의 계절적 요인 분석"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>부동산 시장은 계절에 따라 거래량과 가격이 달라지는 경향이 있어요. 예를 들어, 봄과 가을에는 이사 수요가 증가하면서 매매나 전세 가격이 상승할 수 있고, 겨울은 거래가 적어 가격이 안정되거나 하락할 가능성이 높아요. 특히, 학군이나 입주 물량 등 지역별 특성에 따라 계절적 영향이 달라질 수 있어요. 계절적 요인을 이해하면 부동산 거래 시점을 더 전략적으로 결정할 수 있죠. 여러분은 계절이 부동산 시장에 미치는 영향을 어떻게 느끼고 계신가요? 의견을 나눠주세요!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"스마트 도시 개발이 부동산 시장에 미치는 영향"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>스마트 도시 개발은 첨단 기술을 활용해 생활 환경을 개선하며 부동산 시장에도 큰 영향을 미쳐요. 예를 들어, 자율주행차 도입, 스마트 빌딩 확산, 공공 와이파이 같은 기술이 적용되면 지역의 주거 가치와 상업용 부동산 수요가 증가할 수 있어요. 또한, 기업 유치와 인구 증가로 지역 경제가 활성화되며 부동산 시장이 활기를 띨 가능성이 크죠. 하지만, 개발이 지연되거나 높은 비용 부담이 발생하면 부정적인 영향을 줄 수도 있어요. 여러분은 스마트 도시 개발이 부동산 시장에 어떤 영향을 미친다고 생각하시나요? 의견을 나눠주세요!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"소상공인 지원 정책, 무엇이 더 필요할까?"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>소상공인 지원 정책은 지역 경제와 일자리 창출에 중요한 역할을 해요. 현재 정부는 대출 지원, 세금 감면, 교육 프로그램 등을 통해 소상공인을 돕고 있지만, 일부에서는 지원이 부족하거나 실질적 효과가 크지 않다는 의견도 있어요. 예를 들어, 대출 지원은 유용하지만 상환 부담이 클 수 있고, 디지털 전환을 위한 지원은 아직 미흡하다는 지적이 있어요. 여러분은 현재 소상공인 지원 정책에 대해 어떻게 생각하시나요? 더 나은 정책을 위해 필요한 점이나 개선 아이디어를 공유해주세요!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"스타트업 지원 정책, 현실과 한계"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>스타트업 지원 정책은 창업 초기 기업들이 성장할 수 있도록 돕는 중요한 역할을 해요. 정부는 자금 지원, 세제 혜택, 창업 공간 제공 등 다양한 방법으로 스타트업을 지원하고 있어요. 하지만 일부에서는 정책이 실질적 효과를 내지 못하거나, 지원 대상 선정이 공정하지 않다는 지적도 있어요. 예를 들어, 창업 자금 지원이 초기 자금난 해소에는 도움이 되지만, 지속적인 성장 지원은 부족하다는 의견이 있죠. 여러분은 현재 스타트업 지원 정책의 장점과 한계에 대해 어떻게 생각하시나요? 개선이 필요한 부분은 무엇일까요? 의견을 나눠주세요!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"공공 서비스 확대가 경제에 미치는 영향"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>공공 서비스 확대는 경제 전반에 긍정적 영향을 줄 수 있는 중요한 정책이에요. 예를 들어, 교육, 의료, 교통 등 공공 서비스를 강화하면 국민의 삶의 질이 향상되고, 노동 생산성이 높아질 수 있어요. 또한, 일자리 창출과 소비 증대 효과로 지역 경제 활성화에 기여하기도 해요. 반면, 재정 부담이 커질 경우 세금 증가나 국가 부채 확대 등 부작용이 생길 수도 있어요. 공공 서비스 확대는 경제 성장을 촉진하는 동시에 재정적 균형이 필요해요. 여러분은 공공 서비스 강화가 경제에 어떤 영향을 미친다고 생각하시나요? 의견을 나눠주세요!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"기술 혁신과 규제, 균형점 찾기"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>기술 혁신은 경제와 산업 발전의 핵심 동력이지만, 규제는 안전성과 공정성을 유지하기 위해 필수적이에요. 예를 들어, 자율주행차, AI 같은 신기술이 도입되면 산업이 빠르게 성장하지만, 규제가 없으면 안전 문제나 독점 문제가 생길 수 있어요. 반면, 과도한 규제는 혁신의 속도를 늦추거나 기업의 경쟁력을 약화시킬 수 있죠. 기술 혁신과 규제는 서로 충돌하지 않으면서도 균형을 유지해야 효과적인데요, 여러분은 신기술 도입과 규제 사이에서 어떤 균형점을 찾아야 한다고 생각하시나요? 의견을 나눠주세요!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://ripple-s3.s3.ap-northeast-2.amazonaws.com/toktok/832ef132-f2f6-4545-854d-23f974e6b145.jpg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://ripple-s3.s3.ap-northeast-2.amazonaws.com/toktok/fa8c4bea-6c8f-4b19-90c1-bbf4f66f1291.jpg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://ripple-s3.s3.ap-northeast-2.amazonaws.com/toktok/fda035b7-3297-4673-b4ff-681cbf234d8b.jpg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://ripple-s3.s3.ap-northeast-2.amazonaws.com/toktok/d0836db4-08c4-4748-bfc1-449d86ab6d27.jpg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://ripple-s3.s3.ap-northeast-2.amazonaws.com/toktok/34afd6e5-a57b-48f7-9f18-830256f0b38b.jpg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://ripple-s3.s3.ap-northeast-2.amazonaws.com/toktok/d302c4ab-4ec8-42d5-a2f4-48df3fc719b5.jpg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://ripple-s3.s3.ap-northeast-2.amazonaws.com/toktok/59d955a2-e503-441d-9770-0845ed6ef68a.jpg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://ripple-s3.s3.ap-northeast-2.amazonaws.com/toktok/7dc221d7-de45-4dd5-a238-7f64bfc9ea49.jpg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://ripple-s3.s3.ap-northeast-2.amazonaws.com/toktok/eb419fa2-0692-4a34-8237-2e91089069f7.jpg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://ripple-s3.s3.ap-northeast-2.amazonaws.com/toktok/f230c45d-fe8e-4067-8ca6-4632b16f05fe.jpg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://ripple-s3.s3.ap-northeast-2.amazonaws.com/toktok/c01fde0d-d979-434f-8a51-5218f0683c7e.jpg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://ripple-s3.s3.ap-northeast-2.amazonaws.com/toktok/d0b54a38-28f7-45dd-8e1a-89f8c1f07f5d.jpg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://ripple-s3.s3.ap-northeast-2.amazonaws.com/toktok/f00ca746-0b5a-41e7-9ff0-5ddc25f20ad8.jpg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://ripple-s3.s3.ap-northeast-2.amazonaws.com/toktok/4d236346-6b2c-4d1f-8f1e-ff4f7453c5b9.jpg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://ripple-s3.s3.ap-northeast-2.amazonaws.com/toktok/60e08635-b5d6-41df-9dca-c12d8599fcbe.jpg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://ripple-s3.s3.ap-northeast-2.amazonaws.com/toktok/da3471b5-6256-4ee7-9efb-38230b5f0816.jpg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://ripple-s3.s3.ap-northeast-2.amazonaws.com/toktok/46ecb045-5bdb-4a08-b581-3d26b7e5228a.jpg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://ripple-s3.s3.ap-northeast-2.amazonaws.com/toktok/839aaa10-f4a6-444b-9192-1821b8d5c60c.jpg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://ripple-s3.s3.ap-northeast-2.amazonaws.com/toktok/3c8babf0-2d28-43d3-97b9-bcd7cb10e8ee.jpg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://ripple-s3.s3.ap-northeast-2.amazonaws.com/toktok/6276d1c4-ecf5-4e89-b954-51694a1748f9.jpg</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -64,7 +306,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -75,6 +317,15 @@
     </font>
     <font>
       <sz val="8"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="12"/>
+      <color theme="10"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
       <charset val="129"/>
@@ -98,21 +349,28 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="하이퍼링크" xfId="1" builtinId="8"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -497,7 +755,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7CDE44A6-9D8C-FF4A-982B-EB4473C6C88A}">
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C21"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -513,7 +771,7 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>4</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="342">
@@ -523,13 +781,244 @@
       <c r="B2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C2">
+      <c r="C2" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="266">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="266">
+      <c r="A4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="266">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="304">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="228">
+      <c r="A7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="266">
+      <c r="A8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="285">
+      <c r="A9" t="s">
         <v>16</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="266">
+      <c r="A10" t="s">
+        <v>18</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="285">
+      <c r="A11" t="s">
+        <v>21</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="266">
+      <c r="A12" t="s">
+        <v>23</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="247">
+      <c r="A13" t="s">
+        <v>25</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="247">
+      <c r="A14" t="s">
+        <v>27</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="228">
+      <c r="A15" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="228">
+      <c r="A16" t="s">
+        <v>31</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="266">
+      <c r="A17" t="s">
+        <v>33</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="247">
+      <c r="A18" t="s">
+        <v>35</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="266">
+      <c r="A19" t="s">
+        <v>37</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="266">
+      <c r="A20" t="s">
+        <v>39</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" ht="247">
+      <c r="A21" t="s">
+        <v>41</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>62</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="C2" r:id="rId1" xr:uid="{860DF8A4-5E59-0249-A9E7-3724F72E9D08}"/>
+    <hyperlink ref="C3" r:id="rId2" xr:uid="{FC6C4962-4163-004C-B780-D44A27CC297A}"/>
+    <hyperlink ref="C4" r:id="rId3" xr:uid="{2D7264D7-9355-8A48-B6D3-AEB23BF3C026}"/>
+    <hyperlink ref="C5" r:id="rId4" xr:uid="{C2F9867C-1DB9-3D41-AED7-C6E7FE147F16}"/>
+    <hyperlink ref="C6" r:id="rId5" xr:uid="{58A905C1-C903-514F-B567-D257D4ED4479}"/>
+    <hyperlink ref="C7" r:id="rId6" xr:uid="{1E3AACF8-3A8D-4643-8F5C-F7EAB242FE53}"/>
+    <hyperlink ref="C8" r:id="rId7" xr:uid="{AEE7B2FC-DF3D-EF49-869D-4D666F021CB4}"/>
+    <hyperlink ref="C9" r:id="rId8" xr:uid="{15454302-14F1-8541-8F8C-32EE388018E0}"/>
+    <hyperlink ref="C10" r:id="rId9" xr:uid="{F962D9B7-F562-D444-B057-1B02D3F92D18}"/>
+    <hyperlink ref="C11" r:id="rId10" xr:uid="{981FCDEA-86D3-4944-BC1D-F723CD7A2601}"/>
+    <hyperlink ref="C12" r:id="rId11" xr:uid="{AB507696-BAD1-3643-8693-079F59403C0D}"/>
+    <hyperlink ref="C13" r:id="rId12" xr:uid="{FF044A40-CDE6-A34D-9A48-6532DFB44BB3}"/>
+    <hyperlink ref="C14" r:id="rId13" xr:uid="{8C477FD7-823A-D14A-9E4C-E0E97AFCA55D}"/>
+    <hyperlink ref="C15" r:id="rId14" xr:uid="{F659ECDF-1143-5E47-A04C-F7B6EF5A4F4F}"/>
+    <hyperlink ref="C16" r:id="rId15" xr:uid="{809FECBD-8E40-484B-AA3B-7AE7E711FA73}"/>
+    <hyperlink ref="C17" r:id="rId16" xr:uid="{0842D135-3266-EE4D-BABD-D624902A6E2E}"/>
+    <hyperlink ref="C18" r:id="rId17" xr:uid="{DDF05539-61B0-154F-9506-13DE053AE0ED}"/>
+    <hyperlink ref="C19" r:id="rId18" xr:uid="{C6335C6F-F36C-7D41-949F-D0BEEADADB57}"/>
+    <hyperlink ref="C20" r:id="rId19" xr:uid="{CBF8825E-DF55-5049-9CA5-221E035FFD7D}"/>
+    <hyperlink ref="C21" r:id="rId20" xr:uid="{A7506E18-7D9F-2443-AE5E-F6252A99A438}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <drawing r:id="rId21"/>
 </worksheet>
 </file>
--- a/src/main/resources/static/excel/toktok.xlsx
+++ b/src/main/resources/static/excel/toktok.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10119"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10608"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jeongchanmin/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7D5D3CD-4C33-ED4D-ADFF-32DB066F6686}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF9A0E11-6232-D04E-9187-362782297F07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="640" yWindow="740" windowWidth="28100" windowHeight="17120" xr2:uid="{D9A326C4-B758-E849-A9AE-141158099DC7}"/>
   </bookViews>
@@ -222,83 +222,82 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>https://ripple-s3.s3.ap-northeast-2.amazonaws.com/toktok/832ef132-f2f6-4545-854d-23f974e6b145.jpg</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://ripple-s3.s3.ap-northeast-2.amazonaws.com/toktok/fa8c4bea-6c8f-4b19-90c1-bbf4f66f1291.jpg</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://ripple-s3.s3.ap-northeast-2.amazonaws.com/toktok/fda035b7-3297-4673-b4ff-681cbf234d8b.jpg</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://ripple-s3.s3.ap-northeast-2.amazonaws.com/toktok/d0836db4-08c4-4748-bfc1-449d86ab6d27.jpg</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://ripple-s3.s3.ap-northeast-2.amazonaws.com/toktok/34afd6e5-a57b-48f7-9f18-830256f0b38b.jpg</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://ripple-s3.s3.ap-northeast-2.amazonaws.com/toktok/d302c4ab-4ec8-42d5-a2f4-48df3fc719b5.jpg</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://ripple-s3.s3.ap-northeast-2.amazonaws.com/toktok/59d955a2-e503-441d-9770-0845ed6ef68a.jpg</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://ripple-s3.s3.ap-northeast-2.amazonaws.com/toktok/7dc221d7-de45-4dd5-a238-7f64bfc9ea49.jpg</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://ripple-s3.s3.ap-northeast-2.amazonaws.com/toktok/eb419fa2-0692-4a34-8237-2e91089069f7.jpg</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://ripple-s3.s3.ap-northeast-2.amazonaws.com/toktok/f230c45d-fe8e-4067-8ca6-4632b16f05fe.jpg</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://ripple-s3.s3.ap-northeast-2.amazonaws.com/toktok/c01fde0d-d979-434f-8a51-5218f0683c7e.jpg</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://ripple-s3.s3.ap-northeast-2.amazonaws.com/toktok/d0b54a38-28f7-45dd-8e1a-89f8c1f07f5d.jpg</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://ripple-s3.s3.ap-northeast-2.amazonaws.com/toktok/f00ca746-0b5a-41e7-9ff0-5ddc25f20ad8.jpg</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://ripple-s3.s3.ap-northeast-2.amazonaws.com/toktok/4d236346-6b2c-4d1f-8f1e-ff4f7453c5b9.jpg</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://ripple-s3.s3.ap-northeast-2.amazonaws.com/toktok/60e08635-b5d6-41df-9dca-c12d8599fcbe.jpg</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://ripple-s3.s3.ap-northeast-2.amazonaws.com/toktok/da3471b5-6256-4ee7-9efb-38230b5f0816.jpg</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://ripple-s3.s3.ap-northeast-2.amazonaws.com/toktok/46ecb045-5bdb-4a08-b581-3d26b7e5228a.jpg</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://ripple-s3.s3.ap-northeast-2.amazonaws.com/toktok/839aaa10-f4a6-444b-9192-1821b8d5c60c.jpg</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://ripple-s3.s3.ap-northeast-2.amazonaws.com/toktok/3c8babf0-2d28-43d3-97b9-bcd7cb10e8ee.jpg</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://ripple-s3.s3.ap-northeast-2.amazonaws.com/toktok/6276d1c4-ecf5-4e89-b954-51694a1748f9.jpg</t>
+    <t>https://ripple-s3.s3.ap-northeast-2.amazonaws.com/toktok/01-1.jpg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://ripple-s3.s3.ap-northeast-2.amazonaws.com/toktok/01-2.jpg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://ripple-s3.s3.ap-northeast-2.amazonaws.com/toktok/01-3.jpg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://ripple-s3.s3.ap-northeast-2.amazonaws.com/toktok/01-4.jpg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://ripple-s3.s3.ap-northeast-2.amazonaws.com/toktok/02-1.jpg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://ripple-s3.s3.ap-northeast-2.amazonaws.com/toktok/02-2.jpg</t>
+  </si>
+  <si>
+    <t>https://ripple-s3.s3.ap-northeast-2.amazonaws.com/toktok/02-3.jpg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://ripple-s3.s3.ap-northeast-2.amazonaws.com/toktok/03-1.jpg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://ripple-s3.s3.ap-northeast-2.amazonaws.com/toktok/03-2.jpg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://ripple-s3.s3.ap-northeast-2.amazonaws.com/toktok/02-4.jpg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://ripple-s3.s3.ap-northeast-2.amazonaws.com/toktok/03-3.jpg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://ripple-s3.s3.ap-northeast-2.amazonaws.com/toktok/03-4.jpg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://ripple-s3.s3.ap-northeast-2.amazonaws.com/toktok/04-1.jpg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://ripple-s3.s3.ap-northeast-2.amazonaws.com/toktok/04-2.jpg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://ripple-s3.s3.ap-northeast-2.amazonaws.com/toktok/04-3.jpg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://ripple-s3.s3.ap-northeast-2.amazonaws.com/toktok/04-4.jpg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://ripple-s3.s3.ap-northeast-2.amazonaws.com/toktok/05-1.jpg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://ripple-s3.s3.ap-northeast-2.amazonaws.com/toktok/05-2.jpg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://ripple-s3.s3.ap-northeast-2.amazonaws.com/toktok/05-3.jpg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://ripple-s3.s3.ap-northeast-2.amazonaws.com/toktok/05-4.jpg</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -859,7 +858,7 @@
         <v>17</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="266">
@@ -870,7 +869,7 @@
         <v>19</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="285">
@@ -881,7 +880,7 @@
         <v>22</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="266">
@@ -997,26 +996,26 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="C2" r:id="rId1" xr:uid="{860DF8A4-5E59-0249-A9E7-3724F72E9D08}"/>
-    <hyperlink ref="C3" r:id="rId2" xr:uid="{FC6C4962-4163-004C-B780-D44A27CC297A}"/>
-    <hyperlink ref="C4" r:id="rId3" xr:uid="{2D7264D7-9355-8A48-B6D3-AEB23BF3C026}"/>
-    <hyperlink ref="C5" r:id="rId4" xr:uid="{C2F9867C-1DB9-3D41-AED7-C6E7FE147F16}"/>
-    <hyperlink ref="C6" r:id="rId5" xr:uid="{58A905C1-C903-514F-B567-D257D4ED4479}"/>
-    <hyperlink ref="C7" r:id="rId6" xr:uid="{1E3AACF8-3A8D-4643-8F5C-F7EAB242FE53}"/>
-    <hyperlink ref="C8" r:id="rId7" xr:uid="{AEE7B2FC-DF3D-EF49-869D-4D666F021CB4}"/>
-    <hyperlink ref="C9" r:id="rId8" xr:uid="{15454302-14F1-8541-8F8C-32EE388018E0}"/>
-    <hyperlink ref="C10" r:id="rId9" xr:uid="{F962D9B7-F562-D444-B057-1B02D3F92D18}"/>
-    <hyperlink ref="C11" r:id="rId10" xr:uid="{981FCDEA-86D3-4944-BC1D-F723CD7A2601}"/>
-    <hyperlink ref="C12" r:id="rId11" xr:uid="{AB507696-BAD1-3643-8693-079F59403C0D}"/>
-    <hyperlink ref="C13" r:id="rId12" xr:uid="{FF044A40-CDE6-A34D-9A48-6532DFB44BB3}"/>
-    <hyperlink ref="C14" r:id="rId13" xr:uid="{8C477FD7-823A-D14A-9E4C-E0E97AFCA55D}"/>
-    <hyperlink ref="C15" r:id="rId14" xr:uid="{F659ECDF-1143-5E47-A04C-F7B6EF5A4F4F}"/>
-    <hyperlink ref="C16" r:id="rId15" xr:uid="{809FECBD-8E40-484B-AA3B-7AE7E711FA73}"/>
-    <hyperlink ref="C17" r:id="rId16" xr:uid="{0842D135-3266-EE4D-BABD-D624902A6E2E}"/>
-    <hyperlink ref="C18" r:id="rId17" xr:uid="{DDF05539-61B0-154F-9506-13DE053AE0ED}"/>
-    <hyperlink ref="C19" r:id="rId18" xr:uid="{C6335C6F-F36C-7D41-949F-D0BEEADADB57}"/>
-    <hyperlink ref="C20" r:id="rId19" xr:uid="{CBF8825E-DF55-5049-9CA5-221E035FFD7D}"/>
-    <hyperlink ref="C21" r:id="rId20" xr:uid="{A7506E18-7D9F-2443-AE5E-F6252A99A438}"/>
+    <hyperlink ref="C3" r:id="rId1" xr:uid="{068F1287-7245-0A47-B455-2AA57D4956DE}"/>
+    <hyperlink ref="C2" r:id="rId2" xr:uid="{11C2CCB7-5755-D74B-8A6A-0C489D444B0D}"/>
+    <hyperlink ref="C4" r:id="rId3" xr:uid="{57C503F9-9F1C-7142-AA08-D30E59E74E1E}"/>
+    <hyperlink ref="C5" r:id="rId4" xr:uid="{8307245D-64CB-C346-BA85-31369FDB2EF2}"/>
+    <hyperlink ref="C6" r:id="rId5" xr:uid="{024085D7-0576-9945-8582-3FADB4F77B81}"/>
+    <hyperlink ref="C7:C21" r:id="rId6" display="https://ripple-s3.s3.ap-northeast-2.amazonaws.com/toktok/02-1.jpg" xr:uid="{6901D44B-1A15-AD40-A77D-BA8C634B764B}"/>
+    <hyperlink ref="C8" r:id="rId7" xr:uid="{64E4B42A-2119-F54B-9E25-DFDB6B2D0996}"/>
+    <hyperlink ref="C9" r:id="rId8" xr:uid="{87D932D1-B496-E848-A848-4FFEF88093CB}"/>
+    <hyperlink ref="C10" r:id="rId9" xr:uid="{837AEBBA-95E8-F84B-B327-3EFC6F81833D}"/>
+    <hyperlink ref="C11" r:id="rId10" xr:uid="{B924D0F9-EB7E-7441-A321-803CDE6D5E0E}"/>
+    <hyperlink ref="C12" r:id="rId11" xr:uid="{35E16F61-1CF6-4F48-8251-DB9F89719B65}"/>
+    <hyperlink ref="C13" r:id="rId12" xr:uid="{0FBF8E6C-AE4D-0045-933F-0E262BB81C40}"/>
+    <hyperlink ref="C14" r:id="rId13" xr:uid="{28B4462E-7E6B-DC49-BF2A-768F2C5AFAE1}"/>
+    <hyperlink ref="C15" r:id="rId14" xr:uid="{9A2DEC85-6E21-A348-AC4B-E6E8D95E032F}"/>
+    <hyperlink ref="C16" r:id="rId15" xr:uid="{FC907B4B-C13A-7544-A305-E4250A15AB5D}"/>
+    <hyperlink ref="C17" r:id="rId16" xr:uid="{D80B66EB-1678-8448-A978-B6DBD364C432}"/>
+    <hyperlink ref="C18" r:id="rId17" xr:uid="{11DAB1C4-3408-5B4B-A92E-CE39AC473882}"/>
+    <hyperlink ref="C19" r:id="rId18" xr:uid="{4802ECCE-0C49-9B4D-93F4-C19ED14A2165}"/>
+    <hyperlink ref="C20" r:id="rId19" xr:uid="{52C63B89-40F5-0646-8BA5-11CA16F052DE}"/>
+    <hyperlink ref="C21" r:id="rId20" xr:uid="{95B8AFFC-8EBD-224A-9DC0-93339A0816AE}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId21"/>
